--- a/cypress/fixtures/File/generated/Annual Maintenance Agreement.xlsx
+++ b/cypress/fixtures/File/generated/Annual Maintenance Agreement.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="82">
   <si>
     <t>name</t>
   </si>
@@ -64,6 +64,12 @@
     <t>Factory GSTIN No.</t>
   </si>
   <si>
+    <t>Registered Office Address</t>
+  </si>
+  <si>
+    <t>Corporate Office Address</t>
+  </si>
+  <si>
     <t>Function</t>
   </si>
   <si>
@@ -157,9 +163,6 @@
     <t>Fixed Term</t>
   </si>
   <si>
-    <t>Initial Renewal Date</t>
-  </si>
-  <si>
     <t>Contract Expiration Date</t>
   </si>
   <si>
@@ -185,6 +188,12 @@
   </si>
   <si>
     <t>Registered Office</t>
+  </si>
+  <si>
+    <t>Counterparty Registered Office Address</t>
+  </si>
+  <si>
+    <t>if Registered office option is selected in above field</t>
   </si>
   <si>
     <t>Counterparty GSTIN No.</t>
@@ -628,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="50" customWidth="1"/>
@@ -717,29 +726,29 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -747,10 +756,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
@@ -758,10 +767,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
@@ -769,10 +778,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
         <v>8</v>
@@ -780,10 +789,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
@@ -791,10 +800,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
         <v>8</v>
@@ -802,21 +811,21 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
@@ -824,79 +833,79 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
         <v>41</v>
-      </c>
-      <c r="B20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" t="s">
         <v>49</v>
       </c>
-      <c r="B24" t="s">
-        <v>44</v>
-      </c>
       <c r="C24" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -904,10 +913,10 @@
         <v>50</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -926,21 +935,21 @@
         <v>52</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" t="s">
         <v>54</v>
       </c>
-      <c r="B28" t="s">
-        <v>14</v>
-      </c>
       <c r="C28" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -959,21 +968,21 @@
         <v>56</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" t="s">
         <v>58</v>
       </c>
-      <c r="B31" t="s">
-        <v>14</v>
-      </c>
       <c r="C31" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -981,7 +990,7 @@
         <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="C32" t="s">
         <v>15</v>
@@ -989,13 +998,13 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1014,7 +1023,7 @@
         <v>63</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C35" t="s">
         <v>8</v>
@@ -1022,7 +1031,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B36" t="s">
         <v>14</v>
@@ -1033,10 +1042,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C37" t="s">
         <v>8</v>
@@ -1058,15 +1067,15 @@
         <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="C39" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B40" t="s">
         <v>14</v>
@@ -1077,7 +1086,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B41" t="s">
         <v>14</v>
@@ -1088,7 +1097,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
@@ -1099,24 +1108,24 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B43" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="C43" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="B44" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="C44" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1124,32 +1133,54 @@
         <v>75</v>
       </c>
       <c r="B45" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" t="s">
         <v>76</v>
       </c>
-      <c r="B46" t="s">
-        <v>73</v>
-      </c>
       <c r="C46" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>78</v>
+      </c>
+      <c r="B47" t="s">
+        <v>76</v>
+      </c>
+      <c r="C47" t="s">
         <v>77</v>
       </c>
-      <c r="B47" t="s">
-        <v>73</v>
-      </c>
-      <c r="C47" t="s">
-        <v>78</v>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>79</v>
+      </c>
+      <c r="B48" t="s">
+        <v>76</v>
+      </c>
+      <c r="C48" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" t="s">
+        <v>76</v>
+      </c>
+      <c r="C49" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
